--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Millennium Systems International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=1acfe6bdf2f2bf38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e36402d35a0e5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d7fadfe6ffe1a94</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e4af396a404624b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c98eb9f81b0fe69d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Data Society</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,54 +2246,54 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,19 +2316,19 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d79dd43d11ec2797</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Systems Analyst 2 (529601691)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Senior QA Automation Engineer New</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Systems Analyst 2 (529601691)</t>
+          <t>AI / ML Engineer - Image Analytics</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>WSP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
+          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer New</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>MDVIP Practice Management</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Analytics Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>MDVIP LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a625dbb46473068</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a625dbb46473068</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Sr. Software Engineer (Full-stack)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>UMB Financial Corporation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer ( Java)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Decatur, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,155 +3356,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Full-stack)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>UMB Financial Corporation</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - NASA</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>INNOVIM, LLC</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Annapolis, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer ( Java)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Press Ganey</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Decatur, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer II-Promo Analytics</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>West Valley City, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
+          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>^Application Support Engineer - 6249380</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4136e0f889e1c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>^Application Support Engineer - 6249380</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,252 +661,252 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a4a649d48f54d4</t>
+          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
+          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,147 +916,147 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
         </is>
       </c>
     </row>
@@ -1068,90 +1068,90 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Data Engineer II-Promo Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>^Application Support Engineer - 6249380</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,277 +1196,277 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4136e0f889e1c8b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>^Application Support Engineer - 6249380</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=83a4a649d48f54d4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>16.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Data Reliability Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28739fe08c3eac0</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c4608a1787de15</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acfe6bdf2f2bf38</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
@@ -1628,20 +1628,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,1652 +1721,3787 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43644f263e6cc15a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
+          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Systems Analyst 2 (529601691)</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
+          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer New</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
+          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI / ML Engineer - Image Analytics</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WSP</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, MLOps, MLflow, CI/CD, Docker, AKS</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c910b7dbb4b17b</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a625dbb46473068</t>
+          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Randa Corp</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full-stack)</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>UMB Financial Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Java)</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Decatur, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer II/III</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Okland Construction</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Veryon</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>TargetPath Solutions</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Avtech Solutions INC.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f28739fe08c3eac0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03c4608a1787de15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Ragle Inc</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>North Richland Hills, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Falls Church, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Specialist Software Engineering - AI Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Transamerica</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Cedar Rapids, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ISPOT</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Software Engineer - .NET / SES</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Securiport</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Software Engineer (Front-End) / APIS</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Securiport</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Software Engineer - .NET / APIS</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Securiport</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer - .NET / TMS</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Securiport</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Intrado</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Longmont, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Data Society</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 2</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ISPOT</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Front End UI Developer (Angular)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Allen Control Systems</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>AAA Central Penn</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Life Advantage</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Data Engineer II New</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>DATAIKU</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Digital Partner</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Cardinal Health</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Systems Analyst 2 (529601691)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LMG Technology Services LLC</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior QA Automation Engineer New</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Advanced software systems</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Chubb Insurance</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Applied AI</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>MDVIP Practice Management</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer, Applied AI</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>MDVIP LLC</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>AAA Central Penn</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test (SDET)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Cayuse</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a625dbb46473068</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Data Engineer- Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>University of Virginia</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
         <v>10.4</v>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0924474206e422da</t>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Cloud/DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer AI</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BMO Financial Group</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer AI</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>BMO Financial Group</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Reyes Coca-Cola Bottling</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Niles, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Randa Corp</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Rosemont, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Full-stack)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>UMB Financial Corporation</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - NASA</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>INNOVIM, LLC</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bf9d965cb61989</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Master Data Management (MDM) Consultant – Profisee Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Excelque</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=9b37c8ee4ee7bf02</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Kimball</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb62521e6f4965d9</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Intrado</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,69 +4406,69 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Data Society</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
@@ -4738,25 +4738,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Systems Analyst 2 (529601691)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,19 +4871,19 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Systems Analyst 2 (529601691)</t>
+          <t>Senior QA Automation Engineer New</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
+          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer New</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
@@ -5018,17 +5018,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MDVIP Practice Management</t>
+          <t>Cayuse</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,77 +5036,77 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55208595c4f43eca</t>
+          <t>https://www.indeed.com/viewjob?jk=0a625dbb46473068</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Applied AI</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MDVIP LLC</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, SQL Server, dbt, Power BI, Python</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31d3f8d013d09</t>
+          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a625dbb46473068</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Senior Data/AI Engineering</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcaed35eb6ac63b</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5395,111 +5395,6 @@
         </is>
       </c>
       <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Full-stack)</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>UMB Financial Corporation</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - NASA</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>INNOVIM, LLC</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Annapolis, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS ARCHITECT - ECOMMERCE</t>
+          <t>Sr Cloud Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage Asset Management</t>
+          <t>Personify Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>York, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f29e7767b416ec2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e55d4c15c9b5aa</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>^Application Support Engineer - 6249380</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4136e0f889e1c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>^Application Support Engineer - 6249380</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a4a649d48f54d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Data Reliability Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Consultant – Profisee Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Excelque</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,102 +1336,102 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b37c8ee4ee7bf02</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer II</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
+          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
+          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
+          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
+          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
+          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
+          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
+          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
+          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
+          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
+          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
+          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
+          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
+          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
+          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
+          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
+          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
+          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
+          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,24 +3461,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3501,19 +3501,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3536,19 +3536,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3571,19 +3571,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3611,112 +3611,112 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Avtech Solutions INC.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3728,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,42 +3741,42 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Avtech Solutions INC.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28739fe08c3eac0</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c4608a1787de15</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Data Society</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,59 +4381,59 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Intrado</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c58d501fbb2c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,19 +4521,19 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4542,11 +4542,11 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Systems Analyst 2 (529601691)</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer New</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer - NASA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cayuse</t>
+          <t>INNOVIM, LLC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5045,356 +5045,6 @@
         </is>
       </c>
       <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a625dbb46473068</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Data Engineer- Microsoft Fabric</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>University of Virginia</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Charlottesville, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Cloud/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer AI</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>BMO Financial Group</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer AI</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>BMO Financial Group</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Broadcom</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Reyes Coca-Cola Bottling</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Niles, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Data/AI Engineering</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcaed35eb6ac63b</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - NASA</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>INNOVIM, LLC</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Annapolis, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II-Promo Analytics</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Data Reliability Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer II</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,29 +1361,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
+          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
+          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
+          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
+          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
+          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
+          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
+          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
+          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
+          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
+          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
+          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
+          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
+          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
+          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
+          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
+          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
+          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
+          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3576,59 +3576,59 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>Avtech Solutions INC.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Avtech Solutions INC.</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4171,42 +4171,42 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
+          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
+          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
+          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
+          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
+          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
+          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
+          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
+          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
+          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
+          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
+          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
+          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
+          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
+          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
+          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
+          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
+          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17235821c3f6bc10</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
+          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
+          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
+          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
+          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
+          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
+          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
+          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
+          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
+          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
+          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
+          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
+          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
+          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
+          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
+          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
+          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
+          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
+          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,59 +3541,59 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>Avtech Solutions INC.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Avtech Solutions INC.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=51a155a2ec6a3efc</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
+          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
+          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
+          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
+          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
+          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
+          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
+          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
+          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
+          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
+          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
+          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
+          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
+          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
+          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
+          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
+          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
+          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
+          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
+          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
         </is>
       </c>
     </row>
@@ -3361,12 +3361,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,59 +3541,59 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Avtech Solutions INC.</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, GCP, Oracle, NoSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3efed3eb4463e7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
@@ -4633,17 +4633,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
@@ -4913,17 +4913,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Randa Corp</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - NASA</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>INNOVIM, LLC</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Hive, Scala, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12bafd41a3bf798f</t>
+          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,557 +1966,557 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
+          <t>https://www.indeed.com/viewjob?jk=51a155a2ec6a3efc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Bioinformatics Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,767 +2526,767 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Data Society</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
+          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
+          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,1755 +3296,110 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Veryon</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>TargetPath Solutions</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51a155a2ec6a3efc</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Ragle Inc</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>North Richland Hills, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Falls Church, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Paychex, Inc.</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Transamerica</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Cedar Rapids, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Sr. Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>ISPOT</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Software Engineer - .NET / SES</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Securiport</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer (Front-End) / APIS</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Securiport</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Engineer - .NET / APIS</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Securiport</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Software Engineer - .NET / TMS</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Securiport</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Menlo Park, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Data Society</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Tommy Car Wash</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Software Development Engineer 2</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>ISPOT</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>AAA Central Penn</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Front End UI Developer (Angular)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Allen Control Systems</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Life Advantage</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Data Engineer II New</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>DATAIKU</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer, Digital Partner</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Cardinal Health</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>AAA Central Penn</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Chubb Insurance</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Data Engineer- Microsoft Fabric</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>University of Virginia</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Charlottesville, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Cloud/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer AI</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>BMO Financial Group</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer AI</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>BMO Financial Group</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Broadcom</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Reyes Coca-Cola Bottling</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Niles, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS ARCHITECT - ECOMMERCE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Storage Asset Management</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>York, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
+          <t>https://www.indeed.com/viewjob?jk=f29e7767b416ec2c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Application Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
+          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>Sr. Application Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Valley City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>West Valley City, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Business Analyst IV)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
+          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
+          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
+          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
+          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer II</t>
+          <t>^Application Support Engineer - 6249380</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4136e0f889e1c8b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>^Application Support Engineer - 6249380</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
+          <t>https://www.indeed.com/viewjob?jk=83a4a649d48f54d4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>Master Data Management (MDM) Consultant – Profisee Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Excelque</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=9b37c8ee4ee7bf02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Data Reliability Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21d0748d1f5a35c3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,24 +1746,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1786,19 +1786,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1821,19 +1821,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1856,212 +1856,212 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a155a2ec6a3efc</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=f28739fe08c3eac0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=03c4608a1787de15</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=51a155a2ec6a3efc</t>
         </is>
       </c>
     </row>
@@ -2188,20 +2188,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bioinformatics Cloud Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
+          <t>Bioinformatics Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Data Society</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3002,11 +3002,11 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chubb Insurance</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
+          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Systems Analyst 2 (529601691)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>LMG Technology Services LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Senior QA Automation Engineer New</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f62a4ead15d94e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Chubb Insurance</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Reyes Coca-Cola Bottling</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Niles, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Randa Corp</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,332 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Cloud/DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M University</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer AI</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BMO Financial Group</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Broadcom</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Reyes Coca-Cola Bottling</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Niles, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data/AI Engineering</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dcaed35eb6ac63b</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Randa Corp</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Rosemont, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer (Full-stack)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>UMB Financial Corporation</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS ARCHITECT - ECOMMERCE</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage Asset Management</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>York, PA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Data Factory</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f29e7767b416ec2c</t>
+          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Application Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
+          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Application Developer</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Valley City, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
+          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>Data Engineer (Business Analyst IV)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>West Valley City, UT, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Analyst IV)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
+          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
+          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
+          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
+          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
+          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
+          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
+          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>^Application Support Engineer - 6249380</t>
+          <t>Data Reliability Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4136e0f889e1c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>^Application Support Engineer - 6249380</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a4a649d48f54d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59ebfd8c1dc1985</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Consultant – Profisee Platform</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Excelque</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b37c8ee4ee7bf02</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer II</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,89 +1441,89 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data Engineer (Brighton MI Office)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Common Sail Investment Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brighton, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,24 +1746,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1786,19 +1786,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1821,247 +1821,247 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TargetPath Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28739fe08c3eac0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c4608a1787de15</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a155a2ec6a3efc</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Bioinformatics Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Data Society</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bioinformatics Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer- Microsoft Fabric</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>University of Virginia</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Cloud Engineer AI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a31f6cd5ddd20bc</t>
+          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Reyes Coca-Cola Bottling</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Niles, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
+          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Systems Analyst 2 (529601691)</t>
+          <t>Sr. Software Engineer (Full-stack)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LMG Technology Services LLC</t>
+          <t>UMB Financial Corporation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3225,496 +3225,6 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior QA Automation Engineer New</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Advanced software systems</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b71302c76e3ba6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Chubb Insurance</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e40475db458220</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>AAA Central Penn</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed22c50a30b76424</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Data Engineer- Microsoft Fabric</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>University of Virginia</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Charlottesville, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Cloud/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer AI</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>BMO Financial Group</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Broadcom</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Reyes Coca-Cola Bottling</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Niles, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Data/AI Engineering</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3dcaed35eb6ac63b</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Full-stack)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>UMB Financial Corporation</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Data Engineer II-Promo Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer II</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Data Reliability Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,69 +1291,69 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,29 +1361,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Full Stack Engineer (C2H)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer (Brighton MI Office)</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Common Sail Investment Group</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brighton, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c780af08dcbda8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
@@ -1908,20 +1908,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe761f1068f25661</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448c5ab4722a01</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer- Microsoft Fabric</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, Scala, SQL Server, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7985ea515039ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer AI</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Cloud Storage, Hadoop, Spark, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552def578ffb19f8</t>
+          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>Sr. Software Engineer (Full-stack)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>UMB Financial Corporation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,155 +3076,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Broadcom</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Reyes Coca-Cola Bottling</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Niles, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9edf8ff72cde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Full-stack)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>UMB Financial Corporation</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Data Reliability Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
+          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer II</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Bioinformatics Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bioinformatics Cloud Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Data Society</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Senior SRE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, Azure, Databricks, Blob Storage, Cloud Storage, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d5ea9eaf910d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
+          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr. Software Engineer (Full-stack)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Randa Corp</t>
+          <t>UMB Financial Corporation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3050,41 +3050,6 @@
         </is>
       </c>
       <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Full-stack)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>UMB Financial Corporation</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Application Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5880998894df386b</t>
+          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Application Developer</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Valley City, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
+          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>Data Engineer (Business Analyst IV)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Valley City, UT, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Analyst IV)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
+          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
+          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
+          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
+          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
+          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
+          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
+          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II-Promo Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
+          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II-Promo Analytics</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Data Reliability Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer II</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,112 +1291,112 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (C2H)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NBCUniversal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ac176083e14a75</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI ML Engineer with Python - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>RV Soft</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
@@ -1611,19 +1611,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,19 +1646,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,137 +1756,137 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TargetPath Solutions</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8cc92d46121bf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Software Engr II - AI/ML OPS Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Bioinformatics Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Software Engineer - .NET / SES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bioinformatics Cloud Engineer</t>
+          <t>Software Engineer (Front-End) / APIS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Software Engineer - .NET / APIS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Securiport</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Software Engineer - .NET / TMS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Data Society</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
+          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - (Hybrid In Office / Remote)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06ca39989d67fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer, Digital Partner</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2652,11 +2652,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
         </is>
       </c>
     </row>
@@ -2678,20 +2678,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior SRE</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, DynamoDB, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d3a17d409d4603</t>
+          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer (Full-stack)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>UMB Financial Corporation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2875,181 +2875,6 @@
         </is>
       </c>
       <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Broadcom</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Full-stack)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>UMB Financial Corporation</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Software Development Engineer - Hasbro Direct</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Allen Control Systems</t>
+          <t>Hasbro, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa444433d6aad59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Allen Control Systems</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8082666934df685b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
@@ -2603,25 +2603,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Digital Partner</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Scala, Data Modeling, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d89c34333b046cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6817702e6d4b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,157 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Broadcom</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc801ed3fb91585</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer (Full-stack)</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>UMB Financial Corporation</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, Scala, PostgreSQL, DynamoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca75ca2f1913297a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI ML Engineer with Python - Remote</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RV Soft</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e188b5e4e75f91</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1721,77 +1721,77 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Software Engineering - AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Bioinformatics Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,112 +2026,112 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engr II - AI/ML OPS Engineer</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e6cd7c52df93861</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bioinformatics Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Data Society</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75b5664a6aff70e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / SES</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb50040f75b1f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer (Front-End) / APIS</t>
+          <t>Data Engineer II New</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>DATAIKU</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6763fb716379185</t>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / APIS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8818c08b495451</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - .NET / TMS</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Securiport</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, SQL Server, MySQL, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae3b24fcb014bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
+          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2350,391 +2350,6 @@
         </is>
       </c>
       <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4b2f2436506efc</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Software Development Engineer 2</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>ISPOT</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, RDS, Scala, Snowflake, MySQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54a4e4c9616d4030</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Sr Software Development Engineer - Hasbro Direct</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Hasbro, Inc.</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Renton, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa444433d6aad59</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Allen Control Systems</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edfae0c05394c576</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Front End UI Developer (Angular)</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Life Advantage</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Data Engineer II New</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>DATAIKU</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Application Developer</t>
+          <t>AWS ARCHITECT - ECOMMERCE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Storage Asset Management</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>York, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
+          <t>https://www.indeed.com/viewjob?jk=f29e7767b416ec2c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>Sr. Application Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>West Valley City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Analyst IV)</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>West Valley City, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
+          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Business Analyst IV)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
+          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
+          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
+          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
+          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
+          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
+          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II-Promo Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
+          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Data Engineer II-Promo Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer II</t>
+          <t>^Application Support Engineer - 6249380</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8055f39b25743ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4136e0f889e1c8b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>^Application Support Engineer - 6249380</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,147 +1266,147 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
+          <t>https://www.indeed.com/viewjob?jk=83a4a649d48f54d4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd43ceac422ce43</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Blob Storage, GCP, BigQuery, Cloud Storage, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ce969ed683c99c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,312 +1756,312 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bioinformatics Cloud Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,207 +2071,207 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Front End UI Developer (Angular)</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Life Advantage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II New</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DATAIKU</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
+          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,40 +2316,1895 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Bismarck, ND, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Frankfort, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Dover, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Concord, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Montpelier, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Helena, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Topeka, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer II/III</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Okland Construction</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Veryon</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f28739fe08c3eac0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03c4608a1787de15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51a155a2ec6a3efc</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Falls Church, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Specialist Software Engineering - AI Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Transamerica</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Cedar Rapids, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Bioinformatics Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Production Control Plane</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Data Society</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Front End UI Developer (Angular)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Life Advantage</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Engineer II New</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DATAIKU</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Systems Analyst 2 (529601691)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>LMG Technology Services LLC</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>Sr Software Engineer</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Randa Corp</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Rosemont, IL, US USA</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D108" t="n">
         <v>10.4</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>

--- a/results/job_matches_2026-04-18.xlsx
+++ b/results/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS ARCHITECT - ECOMMERCE</t>
+          <t>Sr. Application Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage Asset Management</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>York, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f29e7767b416ec2c</t>
+          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Application Developer</t>
+          <t>Data Architect Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Intermountain Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Valley City, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968fc98d620e2089</t>
+          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect Senior</t>
+          <t>Data Engineer (Business Analyst IV)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intermountain Health</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Valley City, UT, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Event Hubs, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90830f129f4d81b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (Business Analyst IV)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, BigQuery, Cloud Storage, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbe1cdbf051393e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6695f94078b3a</t>
+          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08adaf0840841479</t>
+          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ae4c57e6ebaab4</t>
+          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=837fcbc8d1c2ec0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f409661e7bf91a9</t>
+          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596629b570074f41</t>
+          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b985856cd8975d</t>
+          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56d704c945084a6e</t>
+          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcab32638cccd3f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3554e94faca87f03</t>
+          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c42f9bad8603859</t>
+          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba619c87117f61bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21028d3a360007d</t>
+          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d471a0fda1a14faf</t>
+          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b540b572849987d6</t>
+          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II-Promo Analytics</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ead1d6aa5dddb</t>
+          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>^Application Support Engineer - 6249380</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4136e0f889e1c8b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>^Application Support Engineer - 6249380</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83a4a649d48f54d4</t>
+          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, MapReduce, HBase, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e8bf364a87bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Business Intelligence Developer II/III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Okland Construction</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
+          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
+          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MLOps, MLflow, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fad382752e6c45e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Springfield, IL, US USA</t>
+          <t>Cheyenne, WY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9613eb2ade378a18</t>
+          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c45f8f708d459eac</t>
+          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Montgomery, AL, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae74230ecf77083</t>
+          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cheyenne, WY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045625da123bda7e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ac2cb123da9211</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Jefferson City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=491a518418efe5a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb028d0699e5bc93</t>
+          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd55914d5888185</t>
+          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jefferson City, MO, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc0e7131432336</t>
+          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d3be4b73d920a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deec05139dabc08a</t>
+          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5550bb7ebf355ee1</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d8d6745d3062a8</t>
+          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Fe, NM, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d40288b2e57fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4280fc6cb28b71</t>
+          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880d7fb467e52950</t>
+          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Santa Fe, NM, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5fd1213b3b70c6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Carson City, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f84b5e1fdb16e36</t>
+          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74f10105ffe043c</t>
+          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd07d601c92ea5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Carson City, NV, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ce5f46b8cd62e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e23fae3491401a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d86d173e08711fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9e35e676e19ee50</t>
+          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08ce97d36c85db</t>
+          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a684bacb673ad34</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4798812a7c7af3</t>
+          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7698457fecc49833</t>
+          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce005b127c47f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=122c1ea0ed721077</t>
+          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Frankfort, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6521a48928704</t>
+          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0409883540b04233</t>
+          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83979e77477c5e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ec46aa032e8c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a86bbd8963f5612</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ba3fa89a3f602</t>
+          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3a46e3d7b83b55b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad20d3e2ae67d22</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9576bfc3d6045509</t>
+          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f2c9d2e9f9ed9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Helena, MT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e05164837c0217</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a46d719bf637e15</t>
+          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9d233e71f6c04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Helena, MT, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc0b0f239ddef48</t>
+          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520fc4e5451ee86e</t>
+          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df2a526495b0fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=298689cf6faee8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Dataflow, Cloud Storage, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ef5f7a924752df</t>
+          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer II/III</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Okland Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95e16a542c86ff4d</t>
+          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3221,19 +3221,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Integration Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3256,19 +3256,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Artificial Intelligence Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3291,212 +3291,212 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28739fe08c3eac0</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,102 +3541,102 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c4608a1787de15</t>
+          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Bioinformatics Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a155a2ec6a3efc</t>
+          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e545552d097b871</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Front End UI Developer (Angular)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b224b645b547d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Life Advantage</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a95a3a6011314bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debfb044aeec9a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Randa Corp</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3750,461 +3750,6 @@
         </is>
       </c>
       <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b6b341f6c861ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Paychex, Inc.</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Specialist Software Engineering - AI Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Transamerica</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Cedar Rapids, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, Spark, PySpark</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fff175ae01f3ab66</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Bioinformatics Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70f3b60b1d9a1fb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Production Control Plane</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Menlo Park, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Data Society</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Flume, Spark, Scala, Kafka, Snowflake, ETL, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1152b9186635df1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Front End UI Developer (Angular)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Life Advantage</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef10f68a09aff48</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Engineer II New</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>DATAIKU</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, DataOps, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26fdda68d597e001</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Systems Analyst 2 (529601691)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>LMG Technology Services LLC</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2af64e3b78cd69</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4b3cab37699f28</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Spark, Scala, ETL, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e04623dda5e67ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Randa Corp</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Rosemont, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Azure, GCP, Scala, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=efdbabb40f26b1d0</t>
         </is>
